--- a/data/processed/positivacao/2024-08_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2024-08_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -26427,7 +26427,7 @@
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B1004" t="inlineStr"/>
@@ -37571,7 +37571,7 @@
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1433" t="inlineStr"/>
@@ -65943,7 +65943,7 @@
     <row r="2525">
       <c r="A2525" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2525" t="inlineStr"/>
@@ -67588,12 +67588,12 @@
       <c r="A2589" t="inlineStr"/>
       <c r="B2589" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 5 cliente(s), não positivou 88 cliente(s) - Total vendido: R$ 8.901,72
+          <t>Vendedor 1 - VENDEDOR 01: positivou 5 cliente(s), não positivou 88 cliente(s) - Total vendido: R$ 8.901,72
 Vendedor 18 - LOJA: positivou 198 cliente(s), não positivou 703 cliente(s) - Total vendido: R$ 76.811,40
-Vendedor 3 - FERNANDA: positivou 100 cliente(s), não positivou 328 cliente(s) - Total vendido: R$ 159.595,93
-Vendedor 4 - DANIELA: positivou 108 cliente(s), não positivou 538 cliente(s) - Total vendido: R$ 55.041,01
+Vendedor 3 - VENDEDOR 03: positivou 100 cliente(s), não positivou 328 cliente(s) - Total vendido: R$ 159.595,93
+Vendedor 4 - VENDEDOR 04: positivou 108 cliente(s), não positivou 538 cliente(s) - Total vendido: R$ 55.041,01
 Vendedor 5 - SITE: positivou 4 cliente(s), não positivou 440 cliente(s) - Total vendido: R$ 1.197,72
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 62 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 62 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2589" t="inlineStr"/>
